--- a/outputs/evaluation/architecture/design/v3/CF_M05/run_3/CF_M05_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/design/v3/CF_M05/run_3/CF_M05_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.6341</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.7536</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.6471</v>
       </c>
       <c r="D3" t="n">
+        <v>0.7586000000000001</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9441000000000001</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.5714</v>
       </c>
       <c r="D4" t="n">
+        <v>0.7272999999999999</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.888</v>
       </c>
     </row>
@@ -1221,14 +1235,11 @@
           <t>57</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Leader Microservice</t>
@@ -1254,13 +1265,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M05_AU01</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1281,7 +1290,6 @@
       <c r="D3" t="n">
         <v>0.806</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1302,7 +1310,6 @@
           <t>['AU_01', 'AU_02']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_21</t>
@@ -1313,7 +1320,6 @@
           <t>client, server</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1332,7 +1338,6 @@
           <t>CF_M05_AU06, CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M05_AU24</t>
@@ -1363,7 +1368,6 @@
       <c r="D4" t="n">
         <v>0.8274</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1384,7 +1388,6 @@
           <t>['AU_05', 'AU_02']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_23</t>
@@ -1395,7 +1398,6 @@
           <t>data access layer, server</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1414,7 +1416,6 @@
           <t>CF_M05_AU21, CF_M05_AU16</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M05_AU26</t>
@@ -1465,14 +1466,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Client(Frontend)</t>
@@ -1498,13 +1496,11 @@
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M05_AU06</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1545,14 +1541,11 @@
           <t>58</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Access Control Microservice</t>
@@ -1577,13 +1570,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M05_AU03</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1624,14 +1615,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Server (Backend)</t>
@@ -1656,13 +1644,11 @@
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1703,14 +1689,11 @@
           <t>57</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Portal Microservice</t>
@@ -1737,13 +1720,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M05_AU02</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1784,14 +1765,11 @@
           <t>59</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Scheduler Microservice</t>
@@ -1820,13 +1798,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M05_AU05</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1867,14 +1843,11 @@
           <t>58</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Communication Log Microservice</t>
@@ -1903,13 +1876,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M05_AU04</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1955,13 +1926,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Presentation Layer (Controllers)</t>
@@ -1987,13 +1956,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M05_AU17</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2039,13 +2006,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Data access layer (Repositories)</t>
@@ -2069,13 +2034,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M05_AU21</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2121,13 +2084,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Domain Layer (Models)</t>
@@ -2152,13 +2113,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M05_AU19</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2179,7 +2138,6 @@
       <c r="D14" t="n">
         <v>0.9514</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -2200,7 +2158,6 @@
           <t>['AU_08', 'AU_02']</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_22</t>
@@ -2211,7 +2168,6 @@
           <t>viewmodel, server</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -2230,7 +2186,6 @@
           <t>CF_M05_AU14, CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M05_AU34</t>
@@ -2286,13 +2241,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Business Logic Layer (Services)</t>
@@ -2316,13 +2269,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M05_AU18</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2343,7 +2294,6 @@
       <c r="D16" t="n">
         <v>0.9671</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -2364,7 +2314,6 @@
           <t>['AU_10', 'AU_11', 'AU_12', 'AU_13', 'AU_14']</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_20</t>
@@ -2375,7 +2324,6 @@
           <t>leader service, portal service, access control service, communication log service, scheduler service</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -2394,7 +2342,6 @@
           <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU11, CF_M05_AU12</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M05_AU22</t>
@@ -2450,13 +2397,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>P_05</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Layered Architecture</t>
@@ -2478,14 +2423,11 @@
       <c r="P17" t="n">
         <v>68.69</v>
       </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2526,14 +2468,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Cloud Architecture</t>
@@ -2553,14 +2492,11 @@
       <c r="P18" t="n">
         <v>60</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M05_P05</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2606,13 +2542,11 @@
           <t>['AU_01']</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>View</t>
@@ -2638,13 +2572,11 @@
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M05_AU13</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2690,13 +2622,11 @@
           <t>['AU_22']</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2721,13 +2651,11 @@
           <t>CF_M05_AU34</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M05_AU31</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2773,13 +2701,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Spring Boot</t>
@@ -2805,13 +2731,11 @@
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M05_AU29</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2857,13 +2781,11 @@
           <t>['AU_01']</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>MVVM</t>
@@ -2883,14 +2805,11 @@
       <c r="P22" t="n">
         <v>62</v>
       </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2936,13 +2855,11 @@
           <t>['AU_01']</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Angular</t>
@@ -2966,13 +2883,11 @@
           <t>CF_M05_AU06</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M05_AU30</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3013,14 +2928,11 @@
           <t>56</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Microservices</t>
@@ -3039,14 +2951,11 @@
       <c r="P24" t="n">
         <v>56</v>
       </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3092,13 +3001,11 @@
           <t>['AU_01']</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Model</t>
@@ -3124,13 +3031,11 @@
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M05_AU15</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3171,14 +3076,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Client-Server</t>
@@ -3199,7 +3101,6 @@
       <c r="P26" t="n">
         <v>61</v>
       </c>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>Design Pattern</t>
@@ -3210,7 +3111,6 @@
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3256,13 +3156,11 @@
           <t>['AU_01']</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>ViewModel</t>
@@ -3288,13 +3186,11 @@
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>CF_M05_AU14</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3368,7 +3264,6 @@
           <t>JSON</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Data format used for message exchange.</t>
@@ -3404,7 +3299,6 @@
           <t>Amazon Web Services</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Cloud provider for the project.</t>
@@ -3496,7 +3390,6 @@
           <t>Amazon EKS</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">For the deployment of the application, Amazon EKS has been used, a service offered by AWS
@@ -3534,7 +3427,6 @@
           <t>SonarQube</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>SonarQube is a
@@ -3573,7 +3465,6 @@
           <t>Grafana</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
@@ -3609,7 +3500,6 @@
           <t>Amazon RDS</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t xml:space="preserve"> the microservices are connected to a shared database (Amazon RDS) that is decoupled per
@@ -3646,7 +3536,6 @@
           <t>Ordering</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>These two microservices are responsible for
@@ -3683,7 +3572,6 @@
           <t>GSB</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>These two microservices are responsible for
@@ -3720,7 +3608,6 @@
           <t>Database</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
@@ -3733,7 +3620,6 @@
           <t>AU_23</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>0.7869</v>
       </c>
@@ -3754,7 +3640,6 @@
           <t>Contract Layer (DTO/Mappers)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Data Transfer Objects (DTOs) act as information containers that allow the data required for each
@@ -3786,7 +3671,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>communication log microservice, leader microservice, portal microservice, access control microservice, scheduler microservice, client(frontend), amazon eks</t>
@@ -3822,7 +3706,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>presentation layer (controllers), data access layer (repositories)</t>
@@ -3838,7 +3721,6 @@
           <t>AU_23</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>0.7479</v>
       </c>
@@ -3854,7 +3736,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>viewmodel, view, model</t>
@@ -3895,7 +3776,6 @@
           <t>REST</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
@@ -3932,7 +3812,6 @@
           <t>Docker</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>The deployment process for our application begins with the creation of a Docker image [28] for each microservice which has its own repository with a Dockerfile [29].</t>
@@ -3968,7 +3847,6 @@
           <t>Kubernetes</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>which allows the use of Kubernetes (K8s), a container orchestration platform created by
@@ -4005,7 +3883,6 @@
           <t>Shared Database</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
@@ -4018,7 +3895,6 @@
           <t>AU_23</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>0.7251</v>
       </c>
